--- a/quizzes/032_surfboard_recommendation_quiz--quizzes.xlsx
+++ b/quizzes/032_surfboard_recommendation_quiz--quizzes.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1121,7 +1121,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C84"/>
+  <dimension ref="A1:C82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="34" customWidth="1" min="1" max="1"/>
@@ -1392,46 +1392,46 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>choppy</t>
+          <t>glassy</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Choppy</t>
+          <t>Glassy</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>wave_condition_choices</t>
+          <t>wave_height_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>choppy</t>
+          <t>small</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Choppy</t>
+          <t>Small</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>wave_condition_choices</t>
+          <t>wave_height_choices</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>glassy</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Glassy</t>
+          <t>Medium</t>
         </is>
       </c>
     </row>
@@ -1443,46 +1443,46 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Small</t>
+          <t>Large</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>wave_height_choices</t>
+          <t>wave_speed_choices</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Medium</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>wave_height_choices</t>
+          <t>wave_speed_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Large</t>
+          <t>3-4</t>
         </is>
       </c>
     </row>
@@ -1494,12 +1494,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>5-6</t>
         </is>
       </c>
     </row>
@@ -1511,46 +1511,46 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>7-8</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>wave_speed_choices</t>
+          <t>preferred_board_type_choices</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>funboard</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>Funboard</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>wave_speed_choices</t>
+          <t>preferred_board_type_choices</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>shortboard</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>Shortboard</t>
         </is>
       </c>
     </row>
@@ -1562,12 +1562,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>funboard</t>
+          <t>longboard</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Funboard</t>
+          <t>Longboard</t>
         </is>
       </c>
     </row>
@@ -1579,46 +1579,46 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>shortboard</t>
+          <t>fishboard</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Shortboard</t>
+          <t>Fishboard</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>preferred_board_type_choices</t>
+          <t>surf_frequency_choices</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>longboard</t>
+          <t>daily</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Longboard</t>
+          <t>Daily</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>preferred_board_type_choices</t>
+          <t>surf_frequency_choices</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>fishboard</t>
+          <t>several_times_a_week</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Fishboard</t>
+          <t>Several times a week</t>
         </is>
       </c>
     </row>
@@ -1630,12 +1630,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>daily</t>
+          <t>several_times_a_month</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Daily</t>
+          <t>Several times a month</t>
         </is>
       </c>
     </row>
@@ -1647,46 +1647,46 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>several_times_a_week</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Several times a week</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>surf_frequency_choices</t>
+          <t>surf_area_choices</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>several_times_a_month</t>
+          <t>beach</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Several times a month</t>
+          <t>Beach</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>surf_frequency_choices</t>
+          <t>surf_area_choices</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>rarely</t>
+          <t>lake</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Rarely</t>
+          <t>Lake</t>
         </is>
       </c>
     </row>
@@ -1698,46 +1698,46 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>beach</t>
+          <t>river</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Beach</t>
+          <t>River</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>surf_area_choices</t>
+          <t>recommended_board_type_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>lake</t>
+          <t>surfboard</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Lake</t>
+          <t>Surfboard</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>surf_area_choices</t>
+          <t>recommended_board_type_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>river</t>
+          <t>funboard</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>River</t>
+          <t>Funboard</t>
         </is>
       </c>
     </row>
@@ -1749,46 +1749,46 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>surfboard</t>
+          <t>longboard</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Surfboard</t>
+          <t>Longboard</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>recommended_board_type_choices</t>
+          <t>recommended_size_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>funboard</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Funboard</t>
+          <t>5.5</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>recommended_board_type_choices</t>
+          <t>recommended_size_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>longboard</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Longboard</t>
+          <t>6.5</t>
         </is>
       </c>
     </row>
@@ -1800,12 +1800,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7.5</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>7.5</t>
         </is>
       </c>
     </row>
@@ -1817,12 +1817,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8.5</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>8.5</t>
         </is>
       </c>
     </row>
@@ -1834,46 +1834,46 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>7.5</t>
+          <t>9.5</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>recommended_size_choices</t>
+          <t>recommended_speed_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>1-2</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>8.5</t>
+          <t>1-2</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>recommended_size_choices</t>
+          <t>recommended_speed_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>3-4</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>3-4</t>
         </is>
       </c>
     </row>
@@ -1885,12 +1885,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>5-6</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>1-2</t>
+          <t>5-6</t>
         </is>
       </c>
     </row>
@@ -1902,46 +1902,46 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>7-8</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>3-4</t>
+          <t>7-8</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>recommended_speed_choices</t>
+          <t>recommended_width_choices</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>5-6</t>
+          <t>22</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>recommended_speed_choices</t>
+          <t>recommended_width_choices</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>7-8</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1953,12 +1953,12 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>22</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1970,46 +1970,46 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>24</t>
+          <t>28</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>recommended_width_choices</t>
+          <t>recommended_fins_choices</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>single</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>26</t>
+          <t>Single</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>recommended_width_choices</t>
+          <t>recommended_fins_choices</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>twin</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>28</t>
+          <t>Twin</t>
         </is>
       </c>
     </row>
@@ -2021,12 +2021,12 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>single</t>
+          <t>thruster</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Single</t>
+          <t>Thruster</t>
         </is>
       </c>
     </row>
@@ -2038,46 +2038,46 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>twin</t>
+          <t>quad</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Twin</t>
+          <t>Quad</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>recommended_fins_choices</t>
+          <t>recommended_tail_type_choices</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>thruster</t>
+          <t>squash</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Thruster</t>
+          <t>Squash</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>recommended_fins_choices</t>
+          <t>recommended_tail_type_choices</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>quad</t>
+          <t>squash_2+1</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Quad</t>
+          <t>Squash 2+1</t>
         </is>
       </c>
     </row>
@@ -2089,12 +2089,12 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>squash</t>
+          <t>square</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Squash</t>
+          <t>Square</t>
         </is>
       </c>
     </row>
@@ -2106,46 +2106,46 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>squash_2+1</t>
+          <t>round</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Squash 2+1</t>
+          <t>Round</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>recommended_tail_type_choices</t>
+          <t>recommended_fins_spacing_choices</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>0-4</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Square</t>
+          <t>0-4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>recommended_tail_type_choices</t>
+          <t>recommended_fins_spacing_choices</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>round</t>
+          <t>5-8</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Round</t>
+          <t>5-8</t>
         </is>
       </c>
     </row>
@@ -2157,46 +2157,46 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>9-12</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>0-4</t>
+          <t>9-12</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>recommended_fins_spacing_choices</t>
+          <t>recommended_fins_size_choices</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>5-8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>5-8</t>
+          <t>4.5</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>recommended_fins_spacing_choices</t>
+          <t>recommended_fins_size_choices</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>9-12</t>
+          <t>6.5</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>9-12</t>
+          <t>6.5</t>
         </is>
       </c>
     </row>
@@ -2208,12 +2208,12 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -2225,114 +2225,114 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>6.5</t>
+          <t>10</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>recommended_fins_size_choices</t>
+          <t>recommended_leash_type_choices</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>leash</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>Leash</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>recommended_fins_size_choices</t>
+          <t>recommended_leash_type_choices</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>no_leash</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>No Leash</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>recommended_leash_type_choices</t>
+          <t>recommended_leash_size_choices</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>leash</t>
+          <t>7-9</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Leash</t>
+          <t>7-9</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>recommended_leash_type_choices</t>
+          <t>recommended_leash_size_choices</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>no_leash</t>
+          <t>9-12</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>No Leash</t>
+          <t>9-12</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>recommended_leash_size_choices</t>
+          <t>recommended_wetsuit_choices</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>no_wetsuit</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>7-9</t>
+          <t>No Wetsuit</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>recommended_leash_size_choices</t>
+          <t>recommended_wetsuit_choices</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>9-12</t>
+          <t>0/2mm</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>9-12</t>
+          <t>0/2mm</t>
         </is>
       </c>
     </row>
@@ -2344,12 +2344,12 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>no_wetsuit</t>
+          <t>2/4mm</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>No Wetsuit</t>
+          <t>2/4mm</t>
         </is>
       </c>
     </row>
@@ -2361,12 +2361,12 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>0/2mm</t>
+          <t>4/6mm</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>0/2mm</t>
+          <t>4/6mm</t>
         </is>
       </c>
     </row>
@@ -2378,180 +2378,146 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>2/4mm</t>
+          <t>6/7mm</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>2/4mm</t>
+          <t>6/7mm</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>recommended_wetsuit_choices</t>
+          <t>recommended_booties_choices</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>4/6mm</t>
+          <t>booties</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>4/6mm</t>
+          <t>Booties</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>recommended_wetsuit_choices</t>
+          <t>recommended_booties_choices</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>6/7mm</t>
+          <t>no_booties</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>6/7mm</t>
+          <t>No Booties</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>recommended_booties_choices</t>
+          <t>recommended_gloves_choices</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>booties</t>
+          <t>gloves</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Booties</t>
+          <t>Gloves</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>recommended_booties_choices</t>
+          <t>recommended_gloves_choices</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>no_booties</t>
+          <t>no_gloves</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>No Booties</t>
+          <t>No Gloves</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>recommended_gloves_choices</t>
+          <t>recommended_hoodie_choices</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>gloves</t>
+          <t>hoodie</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Gloves</t>
+          <t>Hoodie</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>recommended_gloves_choices</t>
+          <t>recommended_hoodie_choices</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>no_gloves</t>
+          <t>no_hoodie</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>No Gloves</t>
+          <t>No Hoodie</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>recommended_hoodie_choices</t>
+          <t>recommended_goggles_choices</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>hoodie</t>
+          <t>goggles</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Hoodie</t>
+          <t>Goggles</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>recommended_hoodie_choices</t>
+          <t>recommended_goggles_choices</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>no_hoodie</t>
+          <t>no_goggles</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
-        <is>
-          <t>No Hoodie</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>recommended_goggles_choices</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>goggles</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Goggles</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>recommended_goggles_choices</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>no_goggles</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
         <is>
           <t>No Goggles</t>
         </is>
